--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.05052117090712</v>
+        <v>9.758209690272409</v>
       </c>
       <c r="D2" t="n">
-        <v>60.81740894016625</v>
+        <v>9.882828952777016</v>
       </c>
       <c r="E2" t="n">
-        <v>9.967099379829213</v>
+        <v>1.619653649222247</v>
       </c>
       <c r="F2" t="n">
-        <v>10.3305431311864</v>
+        <v>1.67871325881779</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.94652416064849</v>
+        <v>7.30381017610538</v>
       </c>
       <c r="D3" t="n">
-        <v>45.33557986812842</v>
+        <v>7.367031728570868</v>
       </c>
       <c r="E3" t="n">
-        <v>9.967099379829213</v>
+        <v>1.619653649222247</v>
       </c>
       <c r="F3" t="n">
-        <v>10.3305431311864</v>
+        <v>1.67871325881779</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.95607715390112</v>
+        <v>5.517862537508933</v>
       </c>
       <c r="D4" t="n">
-        <v>34.77309503922032</v>
+        <v>5.650627943873302</v>
       </c>
       <c r="E4" t="n">
-        <v>9.967099379829213</v>
+        <v>1.619653649222247</v>
       </c>
       <c r="F4" t="n">
-        <v>10.3305431311864</v>
+        <v>1.67871325881779</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.14958193381151</v>
+        <v>4.574307064244372</v>
       </c>
       <c r="D5" t="n">
-        <v>27.33072762012265</v>
+        <v>4.441243238269931</v>
       </c>
       <c r="E5" t="n">
-        <v>9.967099379829213</v>
+        <v>1.619653649222247</v>
       </c>
       <c r="F5" t="n">
-        <v>10.3305431311864</v>
+        <v>1.67871325881779</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.98386252382799</v>
+        <v>6.984877660122049</v>
       </c>
       <c r="D6" t="n">
-        <v>42.16794134995173</v>
+        <v>6.852290469367157</v>
       </c>
       <c r="E6" t="n">
-        <v>9.967099379829213</v>
+        <v>1.619653649222247</v>
       </c>
       <c r="F6" t="n">
-        <v>10.3305431311864</v>
+        <v>1.67871325881779</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.81281642481766</v>
+        <v>6.46958266903287</v>
       </c>
       <c r="D7" t="n">
-        <v>39.04680759241565</v>
+        <v>6.345106233767544</v>
       </c>
       <c r="E7" t="n">
-        <v>9.967099379829213</v>
+        <v>1.619653649222247</v>
       </c>
       <c r="F7" t="n">
-        <v>10.3305431311864</v>
+        <v>1.67871325881779</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
